--- a/data/trans_bre/P16A_n_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 13,62</t>
+          <t>5,12; 13,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 19,9</t>
+          <t>9,52; 19,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 19,61</t>
+          <t>9,7; 19,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 13,63</t>
+          <t>-1,02; 13,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,0; 90,79</t>
+          <t>26,36; 89,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,4; 79,24</t>
+          <t>31,94; 77,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,28; 97,98</t>
+          <t>39,18; 99,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 45,44</t>
+          <t>-1,67; 43,99</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 14,71</t>
+          <t>6,62; 14,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 17,31</t>
+          <t>8,57; 17,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 14,65</t>
+          <t>6,56; 14,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,2; 29,67</t>
+          <t>12,77; 30,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,13; 90,93</t>
+          <t>32,64; 89,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,79; 78,25</t>
+          <t>32,06; 77,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,08; 69,04</t>
+          <t>25,14; 68,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,37; 259,68</t>
+          <t>47,53; 246,52</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 19,36</t>
+          <t>10,23; 19,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,63; 21,71</t>
+          <t>11,61; 21,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 13,56</t>
+          <t>4,51; 13,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 43,97</t>
+          <t>4,64; 45,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,52; 136,06</t>
+          <t>55,04; 137,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,92; 109,43</t>
+          <t>46,36; 108,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,33; 69,14</t>
+          <t>19,16; 73,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,81; 153,76</t>
+          <t>14,95; 158,8</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 18,19</t>
+          <t>10,34; 17,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 19,09</t>
+          <t>10,23; 19,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 17,54</t>
+          <t>9,29; 17,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 12,37</t>
+          <t>-0,06; 13,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,33; 114,31</t>
+          <t>53,19; 112,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,96; 78,11</t>
+          <t>35,46; 79,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,79; 78,98</t>
+          <t>34,49; 75,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 41,37</t>
+          <t>0,13; 44,04</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 14,29</t>
+          <t>10,28; 14,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,36; 17,04</t>
+          <t>12,7; 17,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,15</t>
+          <t>9,81; 14,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,26; 25,61</t>
+          <t>9,57; 26,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,07; 87,17</t>
+          <t>55,17; 85,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,57; 70,25</t>
+          <t>47,83; 70,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,84; 64,91</t>
+          <t>40,75; 65,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,04; 102,23</t>
+          <t>32,27; 106,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,85</t>
+          <t>10,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 13,61</t>
+          <t>4,74; 13,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 19,24</t>
+          <t>9,2; 19,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 19,72</t>
+          <t>9,05; 19,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 13,05</t>
+          <t>5,49; 14,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,36; 89,4</t>
+          <t>25,4; 89,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,94; 77,76</t>
+          <t>30,84; 78,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,18; 99,54</t>
+          <t>35,96; 95,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 43,99</t>
+          <t>15,56; 51,85</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,56</t>
+          <t>13,93</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 14,8</t>
+          <t>6,68; 14,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 17,23</t>
+          <t>8,86; 17,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,61</t>
+          <t>6,81; 14,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 30,14</t>
+          <t>9,92; 17,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,64; 89,99</t>
+          <t>33,08; 88,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,06; 77,94</t>
+          <t>33,98; 76,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,14; 68,29</t>
+          <t>26,5; 68,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,53; 246,52</t>
+          <t>34,99; 75,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,36</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 19,36</t>
+          <t>9,99; 18,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 21,52</t>
+          <t>11,85; 21,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 13,67</t>
+          <t>4,57; 13,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 45,48</t>
+          <t>2,78; 11,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,04; 137,64</t>
+          <t>52,53; 130,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,36; 108,9</t>
+          <t>48,34; 107,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,16; 73,38</t>
+          <t>19,68; 73,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,95; 158,8</t>
+          <t>8,22; 44,06</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>10,47</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,34; 17,86</t>
+          <t>10,45; 17,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 19,13</t>
+          <t>10,96; 19,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 17,1</t>
+          <t>9,15; 17,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 13,21</t>
+          <t>6,52; 14,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,19; 112,58</t>
+          <t>52,79; 110,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,46; 79,82</t>
+          <t>37,62; 79,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,49; 75,07</t>
+          <t>34,94; 79,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 44,04</t>
+          <t>19,61; 50,33</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,96</t>
+          <t>10,82</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 14,27</t>
+          <t>10,24; 14,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,7; 17,22</t>
+          <t>12,46; 17,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,21</t>
+          <t>9,57; 13,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,57; 26,2</t>
+          <t>8,66; 12,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,17; 85,78</t>
+          <t>56,14; 86,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,83; 70,69</t>
+          <t>47,26; 70,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,75; 65,39</t>
+          <t>39,75; 63,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,27; 106,48</t>
+          <t>27,89; 45,39</t>
         </is>
       </c>
     </row>
